--- a/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
+++ b/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
@@ -46,13 +46,13 @@
     <t>R2_ADJUSTED</t>
   </si>
   <si>
-    <t>ALVESPIMYCIN (BRD:BRD-K83988098-001-02-0)</t>
-  </si>
-  <si>
-    <t>DOCETAXEL (BRD:BRD-K30577245-001-05-0)</t>
-  </si>
-  <si>
-    <t>PACLITAXEL (BRD:BRD-K62008436-001-23-9)</t>
+    <t>ALVESPIMYCIN</t>
+  </si>
+  <si>
+    <t>DOCETAXEL</t>
+  </si>
+  <si>
+    <t>PACLITAXEL</t>
   </si>
 </sst>
 </file>
@@ -436,19 +436,19 @@
         <v>0.02376920804593734</v>
       </c>
       <c r="F2">
-        <v>-1.333994179699462</v>
+        <v>-1.334088850429385</v>
       </c>
       <c r="G2">
-        <v>0.0005577485302756556</v>
+        <v>0.0005576309431055731</v>
       </c>
       <c r="H2">
-        <v>0.001171014544306001</v>
+        <v>0.001152466233241958</v>
       </c>
       <c r="I2">
-        <v>0.9479574511461442</v>
+        <v>0.9483821836957677</v>
       </c>
       <c r="J2">
-        <v>0.2919121900328989</v>
+        <v>0.2919109468727583</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -468,19 +468,19 @@
         <v>0.03781630486866031</v>
       </c>
       <c r="F3">
-        <v>-2.129480745523511</v>
+        <v>-2.129591453483396</v>
       </c>
       <c r="G3">
-        <v>0.0005145470400480084</v>
+        <v>0.0005145182399699321</v>
       </c>
       <c r="H3">
-        <v>-0.01700506826319598</v>
+        <v>-0.01688111635459211</v>
       </c>
       <c r="I3">
-        <v>0.5506567643939625</v>
+        <v>0.5504787501086158</v>
       </c>
       <c r="J3">
-        <v>0.2582295486554402</v>
+        <v>0.2582355252083368</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -500,19 +500,19 @@
         <v>0.05934970758237096</v>
       </c>
       <c r="F4">
-        <v>-2.052819609213991</v>
+        <v>-2.053034236769169</v>
       </c>
       <c r="G4">
-        <v>0.00122799330209225</v>
+        <v>0.00122721581171718</v>
       </c>
       <c r="H4">
-        <v>-0.02079345834516124</v>
+        <v>-0.02064965006708083</v>
       </c>
       <c r="I4">
-        <v>0.4861457549306941</v>
+        <v>0.4857857602097495</v>
       </c>
       <c r="J4">
-        <v>0.2169365704420222</v>
+        <v>0.2169524566152229</v>
       </c>
     </row>
   </sheetData>

--- a/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
+++ b/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
@@ -436,19 +436,19 @@
         <v>0.02376920804593734</v>
       </c>
       <c r="F2">
-        <v>-1.334088850429385</v>
+        <v>-1.334088850429382</v>
       </c>
       <c r="G2">
-        <v>0.0005576309431055731</v>
+        <v>0.000557630943105573</v>
       </c>
       <c r="H2">
-        <v>0.001152466233241958</v>
+        <v>0.001152466233242125</v>
       </c>
       <c r="I2">
-        <v>0.9483821836957677</v>
+        <v>0.9483821836957601</v>
       </c>
       <c r="J2">
-        <v>0.2919109468727583</v>
+        <v>0.2919109468727589</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -468,19 +468,19 @@
         <v>0.03781630486866031</v>
       </c>
       <c r="F3">
-        <v>-2.129591453483396</v>
+        <v>-2.129591453483393</v>
       </c>
       <c r="G3">
-        <v>0.0005145182399699321</v>
+        <v>0.0005145182399699296</v>
       </c>
       <c r="H3">
-        <v>-0.01688111635459211</v>
+        <v>-0.01688111635459181</v>
       </c>
       <c r="I3">
-        <v>0.5504787501086158</v>
+        <v>0.5504787501086226</v>
       </c>
       <c r="J3">
-        <v>0.2582355252083368</v>
+        <v>0.2582355252083365</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -500,19 +500,19 @@
         <v>0.05934970758237096</v>
       </c>
       <c r="F4">
-        <v>-2.053034236769169</v>
+        <v>-2.053034236769166</v>
       </c>
       <c r="G4">
-        <v>0.00122721581171718</v>
+        <v>0.001227215811717171</v>
       </c>
       <c r="H4">
-        <v>-0.02064965006708083</v>
+        <v>-0.02064965006708046</v>
       </c>
       <c r="I4">
-        <v>0.4857857602097495</v>
+        <v>0.4857857602097563</v>
       </c>
       <c r="J4">
-        <v>0.2169524566152229</v>
+        <v>0.2169524566152231</v>
       </c>
     </row>
   </sheetData>

--- a/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
+++ b/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
@@ -436,19 +436,19 @@
         <v>0.02376920804593734</v>
       </c>
       <c r="F2">
-        <v>-1.334088850429382</v>
+        <v>-1.334088850429383</v>
       </c>
       <c r="G2">
-        <v>0.000557630943105573</v>
+        <v>0.000557630943105581</v>
       </c>
       <c r="H2">
-        <v>0.001152466233242125</v>
+        <v>0.001152466233242264</v>
       </c>
       <c r="I2">
-        <v>0.9483821836957601</v>
+        <v>0.9483821836957539</v>
       </c>
       <c r="J2">
-        <v>0.2919109468727589</v>
+        <v>0.2919109468727582</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -468,19 +468,19 @@
         <v>0.03781630486866031</v>
       </c>
       <c r="F3">
-        <v>-2.129591453483393</v>
+        <v>-2.129591453483394</v>
       </c>
       <c r="G3">
-        <v>0.0005145182399699296</v>
+        <v>0.0005145182399699333</v>
       </c>
       <c r="H3">
-        <v>-0.01688111635459181</v>
+        <v>-0.01688111635459173</v>
       </c>
       <c r="I3">
-        <v>0.5504787501086226</v>
+        <v>0.5504787501086241</v>
       </c>
       <c r="J3">
-        <v>0.2582355252083365</v>
+        <v>0.2582355252083367</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -500,19 +500,19 @@
         <v>0.05934970758237096</v>
       </c>
       <c r="F4">
-        <v>-2.053034236769166</v>
+        <v>-2.053034236769168</v>
       </c>
       <c r="G4">
-        <v>0.001227215811717171</v>
+        <v>0.00122721581171718</v>
       </c>
       <c r="H4">
-        <v>-0.02064965006708046</v>
+        <v>-0.0206496500670804</v>
       </c>
       <c r="I4">
-        <v>0.4857857602097563</v>
+        <v>0.4857857602097577</v>
       </c>
       <c r="J4">
-        <v>0.2169524566152231</v>
+        <v>0.2169524566152229</v>
       </c>
     </row>
   </sheetData>

--- a/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
+++ b/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
@@ -436,19 +436,19 @@
         <v>0.02376920804593734</v>
       </c>
       <c r="F2">
-        <v>-1.334088850429383</v>
+        <v>-1.334088850429382</v>
       </c>
       <c r="G2">
-        <v>0.000557630943105581</v>
+        <v>0.0005576309431055797</v>
       </c>
       <c r="H2">
-        <v>0.001152466233242264</v>
+        <v>0.001152466233242361</v>
       </c>
       <c r="I2">
-        <v>0.9483821836957539</v>
+        <v>0.9483821836957496</v>
       </c>
       <c r="J2">
-        <v>0.2919109468727582</v>
+        <v>0.2919109468727588</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -471,13 +471,13 @@
         <v>-2.129591453483394</v>
       </c>
       <c r="G3">
-        <v>0.0005145182399699333</v>
+        <v>0.0005145182399699345</v>
       </c>
       <c r="H3">
-        <v>-0.01688111635459173</v>
+        <v>-0.01688111635459176</v>
       </c>
       <c r="I3">
-        <v>0.5504787501086241</v>
+        <v>0.5504787501086237</v>
       </c>
       <c r="J3">
         <v>0.2582355252083367</v>
@@ -500,7 +500,7 @@
         <v>0.05934970758237096</v>
       </c>
       <c r="F4">
-        <v>-2.053034236769168</v>
+        <v>-2.053034236769167</v>
       </c>
       <c r="G4">
         <v>0.00122721581171718</v>
@@ -509,10 +509,10 @@
         <v>-0.0206496500670804</v>
       </c>
       <c r="I4">
-        <v>0.4857857602097577</v>
+        <v>0.4857857602097578</v>
       </c>
       <c r="J4">
-        <v>0.2169524566152229</v>
+        <v>0.216952456615223</v>
       </c>
     </row>
   </sheetData>

--- a/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
+++ b/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
@@ -436,19 +436,19 @@
         <v>0.02376920804593734</v>
       </c>
       <c r="F2">
-        <v>-1.334088850429382</v>
+        <v>-1.334088850429385</v>
       </c>
       <c r="G2">
-        <v>0.0005576309431055797</v>
+        <v>0.0005576309431055744</v>
       </c>
       <c r="H2">
-        <v>0.001152466233242361</v>
+        <v>0.001152466233242347</v>
       </c>
       <c r="I2">
-        <v>0.9483821836957496</v>
+        <v>0.9483821836957501</v>
       </c>
       <c r="J2">
-        <v>0.2919109468727588</v>
+        <v>0.2919109468727583</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -468,16 +468,16 @@
         <v>0.03781630486866031</v>
       </c>
       <c r="F3">
-        <v>-2.129591453483394</v>
+        <v>-2.129591453483396</v>
       </c>
       <c r="G3">
-        <v>0.0005145182399699345</v>
+        <v>0.0005145182399699321</v>
       </c>
       <c r="H3">
-        <v>-0.01688111635459176</v>
+        <v>-0.01688111635459162</v>
       </c>
       <c r="I3">
-        <v>0.5504787501086237</v>
+        <v>0.5504787501086266</v>
       </c>
       <c r="J3">
         <v>0.2582355252083367</v>
@@ -500,19 +500,19 @@
         <v>0.05934970758237096</v>
       </c>
       <c r="F4">
-        <v>-2.053034236769167</v>
+        <v>-2.05303423676917</v>
       </c>
       <c r="G4">
-        <v>0.00122721581171718</v>
+        <v>0.001227215811717174</v>
       </c>
       <c r="H4">
-        <v>-0.0206496500670804</v>
+        <v>-0.02064965006708025</v>
       </c>
       <c r="I4">
-        <v>0.4857857602097578</v>
+        <v>0.4857857602097602</v>
       </c>
       <c r="J4">
-        <v>0.216952456615223</v>
+        <v>0.2169524566152231</v>
       </c>
     </row>
   </sheetData>

--- a/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
+++ b/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
@@ -436,19 +436,19 @@
         <v>0.02376920804593734</v>
       </c>
       <c r="F2">
-        <v>-1.334088850429385</v>
+        <v>-1.334088850429382</v>
       </c>
       <c r="G2">
-        <v>0.0005576309431055744</v>
+        <v>0.0005576309431055834</v>
       </c>
       <c r="H2">
-        <v>0.001152466233242347</v>
+        <v>0.001152466233242506</v>
       </c>
       <c r="I2">
-        <v>0.9483821836957501</v>
+        <v>0.948382183695743</v>
       </c>
       <c r="J2">
-        <v>0.2919109468727583</v>
+        <v>0.2919109468727582</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -468,16 +468,16 @@
         <v>0.03781630486866031</v>
       </c>
       <c r="F3">
-        <v>-2.129591453483396</v>
+        <v>-2.129591453483394</v>
       </c>
       <c r="G3">
-        <v>0.0005145182399699321</v>
+        <v>0.0005145182399699345</v>
       </c>
       <c r="H3">
-        <v>-0.01688111635459162</v>
+        <v>-0.01688111635459147</v>
       </c>
       <c r="I3">
-        <v>0.5504787501086266</v>
+        <v>0.5504787501086299</v>
       </c>
       <c r="J3">
         <v>0.2582355252083367</v>
@@ -500,16 +500,16 @@
         <v>0.05934970758237096</v>
       </c>
       <c r="F4">
-        <v>-2.05303423676917</v>
+        <v>-2.053034236769166</v>
       </c>
       <c r="G4">
-        <v>0.001227215811717174</v>
+        <v>0.001227215811717185</v>
       </c>
       <c r="H4">
-        <v>-0.02064965006708025</v>
+        <v>-0.0206496500670802</v>
       </c>
       <c r="I4">
-        <v>0.4857857602097602</v>
+        <v>0.4857857602097616</v>
       </c>
       <c r="J4">
         <v>0.2169524566152231</v>

--- a/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
+++ b/results/PRISM/prism_candidates_adjusted_proliferation.xlsx
@@ -439,16 +439,16 @@
         <v>-1.334088850429382</v>
       </c>
       <c r="G2">
-        <v>0.0005576309431055834</v>
+        <v>0.0005576309431055693</v>
       </c>
       <c r="H2">
-        <v>0.001152466233242506</v>
+        <v>0.001152466233242222</v>
       </c>
       <c r="I2">
-        <v>0.948382183695743</v>
+        <v>0.9483821836957558</v>
       </c>
       <c r="J2">
-        <v>0.2919109468727582</v>
+        <v>0.2919109468727585</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -468,19 +468,19 @@
         <v>0.03781630486866031</v>
       </c>
       <c r="F3">
-        <v>-2.129591453483394</v>
+        <v>-2.12959145348339</v>
       </c>
       <c r="G3">
-        <v>0.0005145182399699345</v>
+        <v>0.0005145182399699321</v>
       </c>
       <c r="H3">
-        <v>-0.01688111635459147</v>
+        <v>-0.01688111635459185</v>
       </c>
       <c r="I3">
-        <v>0.5504787501086299</v>
+        <v>0.5504787501086216</v>
       </c>
       <c r="J3">
-        <v>0.2582355252083367</v>
+        <v>0.2582355252083364</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -500,19 +500,19 @@
         <v>0.05934970758237096</v>
       </c>
       <c r="F4">
-        <v>-2.053034236769166</v>
+        <v>-2.053034236769165</v>
       </c>
       <c r="G4">
-        <v>0.001227215811717185</v>
+        <v>0.001227215811717171</v>
       </c>
       <c r="H4">
-        <v>-0.0206496500670802</v>
+        <v>-0.02064965006708054</v>
       </c>
       <c r="I4">
-        <v>0.4857857602097616</v>
+        <v>0.4857857602097548</v>
       </c>
       <c r="J4">
-        <v>0.2169524566152231</v>
+        <v>0.2169524566152229</v>
       </c>
     </row>
   </sheetData>
